--- a/StructureDefinition-HivPrepProductPrescription.xlsx
+++ b/StructureDefinition-HivPrepProductPrescription.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T18:57:20+00:00</t>
+    <t>2024-08-18T19:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivPrepProductPrescription.xlsx
+++ b/StructureDefinition-HivPrepProductPrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T19:14:17+00:00</t>
+    <t>2024-10-17T13:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivPrepProductPrescription.xlsx
+++ b/StructureDefinition-HivPrepProductPrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T13:36:11+00:00</t>
+    <t>2024-10-30T19:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivPrepProductPrescription.xlsx
+++ b/StructureDefinition-HivPrepProductPrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T19:02:49+00:00</t>
+    <t>2024-11-07T20:59:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
